--- a/CLASS/SS3/Chemistry/results.xlsx
+++ b/CLASS/SS3/Chemistry/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rabiu Idris Muhammad</t>
+          <t>Ahmad Hasfat Yusuf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>std413</t>
+          <t>std378</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SS3_B</t>
+          <t>SS3_GOLD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,11 +486,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -502,136 +502,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-12-03 14:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Abubakar Fatima Shehu</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>std356</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SS3_GOLD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CHEMISTRY</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2025-12-04 07:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Maryam Jolayemi Ibukunoluwa</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>std843</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SS3_B</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CHEMISTRY</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2025-12-06 15:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Yahaya Aisha Dangana</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>std338</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SS3_GOLD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CHEMISTRY</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2025-12-06 15:57</t>
+          <t>2025-12-07 00:46</t>
         </is>
       </c>
     </row>
